--- a/artfynd/A 21652-2026 artfynd.xlsx
+++ b/artfynd/A 21652-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133263101</v>
       </c>
       <c r="B2" t="n">
-        <v>106828</v>
+        <v>106830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21652-2026 artfynd.xlsx
+++ b/artfynd/A 21652-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133263101</v>
       </c>
       <c r="B2" t="n">
-        <v>106830</v>
+        <v>106838</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 21652-2026 artfynd.xlsx
+++ b/artfynd/A 21652-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,38 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133263101</v>
+        <v>133263079</v>
       </c>
       <c r="B2" t="n">
-        <v>106876</v>
+        <v>75354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220785</v>
+        <v>6427</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Leight.) Frisch &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -777,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133263229</v>
+        <v>133263381</v>
       </c>
       <c r="B3" t="n">
-        <v>58461</v>
+        <v>57280</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -854,6 +853,11 @@
           <t>2026-05-09</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>landade 100 bort</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -878,10 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133263381</v>
+        <v>133263229</v>
       </c>
       <c r="B4" t="n">
-        <v>57280</v>
+        <v>58461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100065</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -955,11 +959,6 @@
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>landade 100 bort</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -981,6 +980,312 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133263101</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Nävlinge V, Sk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>426804</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6213736</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133263074</v>
+      </c>
+      <c r="B6" t="n">
+        <v>104878</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221178</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bäckbräsma</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cardamine amara</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Nävlinge V, Sk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>426804</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6213736</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133263157</v>
+      </c>
+      <c r="B7" t="n">
+        <v>103907</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Nävlinge V, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>426804</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6213736</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nävlinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21652-2026 artfynd.xlsx
+++ b/artfynd/A 21652-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263079</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263229</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263101</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263074</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,8 +1316,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133263157</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>